--- a/data/trans_dic/P17G_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P17G_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un médico de la seguridad social en su última visita</t>
+          <t>Población que consultó en las últimas 2 semanas a un/a médico/a de la seguridad social (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>78,19; 96,8</t>
+          <t>79,6; 96,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>77,32; 96,36</t>
+          <t>76,93; 96,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82,7; 97,03</t>
+          <t>83,15; 97,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50,65; 100,0</t>
+          <t>46,36; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,63; 97,46</t>
+          <t>85,58; 97,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,64; 99,0</t>
+          <t>90,74; 98,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,29; 99,01</t>
+          <t>91,56; 99,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>78,5; 98,16</t>
+          <t>79,44; 97,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>86,41; 95,74</t>
+          <t>85,82; 95,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87,84; 96,78</t>
+          <t>87,86; 96,79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90,54; 97,72</t>
+          <t>90,54; 97,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>73,71; 96,02</t>
+          <t>74,33; 95,9</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>71,2; 90,36</t>
+          <t>70,52; 90,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>88,05; 97,27</t>
+          <t>87,46; 97,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73,41; 90,36</t>
+          <t>73,16; 89,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73,31; 94,48</t>
+          <t>73,11; 95,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>82,99; 93,94</t>
+          <t>83,09; 93,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,58; 98,05</t>
+          <t>90,58; 97,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,91; 94,83</t>
+          <t>84,56; 94,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>81,21; 97,92</t>
+          <t>82,22; 98,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>82,02; 91,01</t>
+          <t>81,35; 91,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91,41; 96,99</t>
+          <t>91,19; 96,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83,08; 91,26</t>
+          <t>82,69; 91,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>82,74; 96,16</t>
+          <t>82,5; 96,01</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80,45; 94,0</t>
+          <t>81,67; 94,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>86,35; 95,61</t>
+          <t>85,91; 95,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86,3; 95,74</t>
+          <t>86,28; 95,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78,87; 94,16</t>
+          <t>78,35; 93,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>88,65; 96,68</t>
+          <t>88,94; 96,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>88,32; 96,56</t>
+          <t>87,46; 96,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>86,6; 94,91</t>
+          <t>86,25; 95,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>81,81; 91,69</t>
+          <t>81,83; 91,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>88,55; 94,95</t>
+          <t>87,95; 94,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>89,16; 95,34</t>
+          <t>88,71; 95,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>88,25; 94,64</t>
+          <t>88,26; 94,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>82,39; 91,58</t>
+          <t>82,18; 91,51</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>75,83; 90,87</t>
+          <t>74,65; 90,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>81,52; 94,62</t>
+          <t>80,56; 94,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81,66; 92,6</t>
+          <t>81,15; 92,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80,45; 92,44</t>
+          <t>79,55; 92,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,26; 96,45</t>
+          <t>87,16; 95,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,68; 99,49</t>
+          <t>95,59; 99,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,16; 95,94</t>
+          <t>87,78; 96,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>81,91; 90,45</t>
+          <t>82,29; 90,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>85,39; 93,2</t>
+          <t>85,4; 93,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91,81; 97,37</t>
+          <t>91,88; 97,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86,7; 93,6</t>
+          <t>86,14; 93,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83,08; 90,25</t>
+          <t>82,85; 89,98</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>85,6; 95,45</t>
+          <t>84,96; 95,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>84,86; 96,53</t>
+          <t>84,86; 96,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,43; 95,63</t>
+          <t>86,04; 95,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87,91; 96,05</t>
+          <t>87,76; 96,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>87,66; 96,42</t>
+          <t>87,06; 96,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>92,59; 98,78</t>
+          <t>93,58; 98,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,62; 96,88</t>
+          <t>88,63; 96,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>85,39; 93,17</t>
+          <t>85,29; 93,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>88,11; 94,62</t>
+          <t>88,44; 95,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91,09; 97,06</t>
+          <t>91,3; 97,12</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89,27; 95,39</t>
+          <t>89,35; 95,5</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>88,33; 93,72</t>
+          <t>88,18; 93,89</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>90,58; 98,01</t>
+          <t>90,69; 97,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>89,23; 98,46</t>
+          <t>89,53; 98,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93,16; 99,27</t>
+          <t>92,94; 99,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84,83; 94,25</t>
+          <t>84,15; 94,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>93,15; 98,83</t>
+          <t>93,25; 98,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>91,59; 98,04</t>
+          <t>91,34; 98,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>89,11; 97,68</t>
+          <t>90,39; 97,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>90,63; 96,59</t>
+          <t>90,45; 96,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93,76; 98,0</t>
+          <t>93,68; 98,07</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>91,75; 97,29</t>
+          <t>92,27; 97,86</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>92,6; 97,67</t>
+          <t>92,73; 97,72</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>89,1; 94,53</t>
+          <t>89,36; 94,86</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>89,49; 99,03</t>
+          <t>89,74; 99,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>95,43; 100,0</t>
+          <t>95,64; 100,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88,53; 98,26</t>
+          <t>88,07; 98,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>89,5; 97,96</t>
+          <t>89,49; 98,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,87; 99,33</t>
+          <t>94,56; 99,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,97; 98,8</t>
+          <t>93,0; 98,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,91; 99,27</t>
+          <t>92,98; 99,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>89,2; 95,74</t>
+          <t>89,12; 96,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>94,1; 98,83</t>
+          <t>94,79; 99,07</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>94,94; 98,94</t>
+          <t>94,73; 98,92</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>93,51; 98,39</t>
+          <t>93,69; 98,47</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,09; 96,16</t>
+          <t>90,82; 96,0</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>88,23; 92,74</t>
+          <t>87,9; 92,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>91,07; 95,09</t>
+          <t>91,05; 94,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89,0; 93,06</t>
+          <t>89,31; 93,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>87,11; 92,11</t>
+          <t>86,85; 92,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>92,25; 95,2</t>
+          <t>91,97; 95,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>94,61; 97,07</t>
+          <t>94,5; 97,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>92,2; 95,22</t>
+          <t>92,14; 95,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>88,42; 92,64</t>
+          <t>88,34; 92,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>91,25; 93,91</t>
+          <t>91,11; 93,78</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>93,64; 95,83</t>
+          <t>93,64; 95,81</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91,45; 93,92</t>
+          <t>91,38; 93,86</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>88,47; 91,88</t>
+          <t>88,34; 91,69</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un médico de la seguridad social en su última visita</t>
+          <t>Población que consultó en las últimas 2 semanas a un/a médico/a de la seguridad social (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>43833; 54268</t>
+          <t>44624; 54240</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>44107; 54969</t>
+          <t>43884; 55003</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55477; 65089</t>
+          <t>55780; 65123</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15807; 31210</t>
+          <t>14469; 31210</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>72746; 82798</t>
+          <t>72704; 82834</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89037; 97243</t>
+          <t>89133; 97241</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>85206; 92416</t>
+          <t>85462; 92414</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>43224; 54048</t>
+          <t>43741; 53944</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>121855; 135013</t>
+          <t>121014; 135127</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136400; 150276</t>
+          <t>136429; 150286</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>145240; 156769</t>
+          <t>145240; 156451</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>63591; 82840</t>
+          <t>64127; 82733</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51872; 65829</t>
+          <t>51374; 65710</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88282; 97528</t>
+          <t>87694; 97591</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66241; 81535</t>
+          <t>66016; 81035</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57655; 74304</t>
+          <t>57498; 74806</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>124957; 141445</t>
+          <t>125104; 140960</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>143473; 155298</t>
+          <t>143470; 154677</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>131777; 147177</t>
+          <t>131238; 146638</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>134908; 162657</t>
+          <t>136572; 163757</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>183242; 203330</t>
+          <t>181759; 203876</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>236431; 250856</t>
+          <t>235878; 250080</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>203899; 223973</t>
+          <t>202950; 225459</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>202506; 235371</t>
+          <t>201917; 234981</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>75461; 88170</t>
+          <t>76610; 88507</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>108449; 120070</t>
+          <t>107888; 120067</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>126838; 140703</t>
+          <t>126798; 140781</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63653; 75989</t>
+          <t>63226; 75767</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>164560; 179470</t>
+          <t>165112; 179066</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>168477; 184209</t>
+          <t>166840; 184149</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>147345; 161477</t>
+          <t>146752; 161830</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>96948; 108649</t>
+          <t>96962; 108685</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>247437; 265324</t>
+          <t>245751; 265103</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>282068; 301618</t>
+          <t>280641; 301485</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>279851; 300122</t>
+          <t>279881; 299763</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>164116; 182420</t>
+          <t>163710; 182290</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>60413; 72395</t>
+          <t>59476; 72328</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>90946; 105553</t>
+          <t>89873; 105314</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>132368; 150105</t>
+          <t>131541; 149856</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>102183; 117402</t>
+          <t>101041; 117080</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>128681; 142235</t>
+          <t>128528; 141435</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>183174; 190473</t>
+          <t>183003; 190486</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>157433; 171319</t>
+          <t>156754; 172158</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>137475; 151821</t>
+          <t>138115; 151516</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>193950; 211694</t>
+          <t>193968; 211426</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>278198; 295039</t>
+          <t>278388; 294930</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>295360; 318871</t>
+          <t>293446; 317239</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>244969; 266099</t>
+          <t>244298; 265296</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>108048; 120483</t>
+          <t>107247; 120668</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>108537; 123471</t>
+          <t>108542; 123449</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>123632; 136797</t>
+          <t>123083; 136776</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>121873; 133159</t>
+          <t>121662; 133378</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>131713; 144873</t>
+          <t>130811; 144387</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>147779; 157662</t>
+          <t>149354; 157694</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>167446; 183060</t>
+          <t>167475; 183109</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>118191; 128962</t>
+          <t>118048; 129050</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>243612; 261590</t>
+          <t>244511; 262641</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>261884; 279062</t>
+          <t>262490; 279237</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>296372; 316685</t>
+          <t>296631; 317051</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>244716; 259641</t>
+          <t>244312; 260108</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>121387; 131332</t>
+          <t>121530; 131307</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>119784; 132176</t>
+          <t>120197; 132069</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>119482; 127317</t>
+          <t>119203; 127323</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>88867; 98737</t>
+          <t>88157; 98499</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>150290; 159455</t>
+          <t>150447; 159500</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>138254; 147992</t>
+          <t>137879; 148015</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>164615; 180442</t>
+          <t>166990; 180094</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>110930; 118223</t>
+          <t>110702; 118505</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>276921; 289441</t>
+          <t>276672; 289654</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>261656; 277467</t>
+          <t>263148; 279087</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>289841; 305703</t>
+          <t>290236; 305851</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>202394; 214724</t>
+          <t>202998; 215486</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>83400; 92291</t>
+          <t>83634; 92299</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>107113; 112239</t>
+          <t>107343; 112239</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>93952; 104275</t>
+          <t>93468; 104436</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>71952; 78758</t>
+          <t>71945; 78850</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>157855; 167044</t>
+          <t>159008; 167091</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>173977; 184888</t>
+          <t>174044; 184922</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>161068; 170266</t>
+          <t>159477; 170252</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>114386; 122768</t>
+          <t>114281; 123176</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>245938; 258296</t>
+          <t>247741; 258923</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>284239; 296201</t>
+          <t>283592; 296140</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>259630; 273169</t>
+          <t>260125; 273398</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>190035; 200612</t>
+          <t>189469; 200288</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>578628; 608216</t>
+          <t>576484; 607664</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>700171; 731094</t>
+          <t>700016; 730239</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>751017; 785293</t>
+          <t>753571; 786816</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>558659; 590780</t>
+          <t>557031; 591366</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>967160; 998057</t>
+          <t>964140; 997163</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1075256; 1103167</t>
+          <t>1074049; 1103455</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1053380; 1087911</t>
+          <t>1052613; 1087723</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>792725; 830583</t>
+          <t>792039; 831417</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1555133; 1600341</t>
+          <t>1552659; 1598206</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1784154; 1825881</t>
+          <t>1784283; 1825624</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1816540; 1865449</t>
+          <t>1815051; 1864231</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1360526; 1413011</t>
+          <t>1358544; 1410118</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P17G_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P17G_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,67%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>79,6; 96,75</t>
+          <t>76,81; 96,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>76,93; 96,42</t>
+          <t>77,37; 96,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83,15; 97,08</t>
+          <t>84,66; 97,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46,36; 100,0</t>
+          <t>49,96; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,58; 97,5</t>
+          <t>86,4; 97,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,74; 98,99</t>
+          <t>89,92; 98,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,56; 99,01</t>
+          <t>91,75; 99,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>79,44; 97,97</t>
+          <t>81,71; 97,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>85,82; 95,82</t>
+          <t>86,05; 95,97</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87,86; 96,79</t>
+          <t>87,33; 96,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90,54; 97,53</t>
+          <t>90,66; 97,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>74,33; 95,9</t>
+          <t>76,14; 96,37</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>87,09%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>70,52; 90,2</t>
+          <t>70,82; 90,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>87,46; 97,33</t>
+          <t>88,03; 97,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73,16; 89,81</t>
+          <t>72,24; 89,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73,11; 95,12</t>
+          <t>75,71; 95,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,09; 93,62</t>
+          <t>83,31; 93,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,58; 97,66</t>
+          <t>89,96; 98,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,56; 94,49</t>
+          <t>85,18; 94,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>82,22; 98,58</t>
+          <t>78,63; 92,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81,35; 91,25</t>
+          <t>82,12; 91,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>91,19; 96,69</t>
+          <t>91,29; 97,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82,69; 91,86</t>
+          <t>82,59; 91,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>82,5; 96,01</t>
+          <t>80,25; 91,86</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>86,21%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81,67; 94,36</t>
+          <t>81,27; 94,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,91; 95,6</t>
+          <t>86,5; 95,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86,28; 95,79</t>
+          <t>85,91; 95,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78,35; 93,89</t>
+          <t>73,19; 91,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>88,94; 96,46</t>
+          <t>88,71; 96,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,46; 96,53</t>
+          <t>87,58; 96,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>86,25; 95,11</t>
+          <t>86,22; 95,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>81,83; 91,72</t>
+          <t>82,6; 91,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>87,95; 94,87</t>
+          <t>88,17; 95,05</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>88,71; 95,3</t>
+          <t>89,16; 95,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>88,26; 94,53</t>
+          <t>88,03; 94,43</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>82,18; 91,51</t>
+          <t>80,95; 90,03</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,96%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>74,65; 90,78</t>
+          <t>74,8; 91,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80,56; 94,4</t>
+          <t>81,77; 94,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81,15; 92,45</t>
+          <t>80,84; 92,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79,55; 92,18</t>
+          <t>81,46; 92,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,16; 95,91</t>
+          <t>87,17; 96,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,59; 99,5</t>
+          <t>95,15; 99,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,78; 96,41</t>
+          <t>87,39; 95,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>82,29; 90,27</t>
+          <t>81,73; 89,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>85,4; 93,08</t>
+          <t>85,03; 93,19</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91,88; 97,34</t>
+          <t>91,88; 97,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86,14; 93,12</t>
+          <t>86,61; 93,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82,85; 89,98</t>
+          <t>83,49; 90,21</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>84,96; 95,59</t>
+          <t>85,32; 95,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>84,86; 96,52</t>
+          <t>84,66; 96,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,04; 95,61</t>
+          <t>86,04; 95,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87,76; 96,21</t>
+          <t>87,67; 96,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>87,06; 96,1</t>
+          <t>86,82; 96,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>93,58; 98,8</t>
+          <t>92,98; 98,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,63; 96,91</t>
+          <t>88,33; 96,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>85,29; 93,24</t>
+          <t>86,01; 93,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>88,44; 95,0</t>
+          <t>88,0; 94,66</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91,3; 97,12</t>
+          <t>91,29; 97,11</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89,35; 95,5</t>
+          <t>89,46; 95,47</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>88,18; 93,89</t>
+          <t>88,22; 93,69</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>90,69; 97,99</t>
+          <t>91,34; 97,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>89,53; 98,38</t>
+          <t>88,83; 98,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>92,94; 99,27</t>
+          <t>92,55; 99,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84,15; 94,02</t>
+          <t>84,23; 94,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>93,25; 98,86</t>
+          <t>93,29; 98,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>91,34; 98,06</t>
+          <t>91,33; 98,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>90,39; 97,49</t>
+          <t>90,33; 97,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>90,45; 96,82</t>
+          <t>90,65; 96,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93,68; 98,07</t>
+          <t>93,63; 97,89</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>92,27; 97,86</t>
+          <t>92,15; 97,56</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>92,73; 97,72</t>
+          <t>92,74; 97,71</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>89,36; 94,86</t>
+          <t>89,6; 95,0</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>89,74; 99,04</t>
+          <t>90,07; 99,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>95,64; 100,0</t>
+          <t>95,71; 100,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88,07; 98,41</t>
+          <t>88,4; 98,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>89,49; 98,08</t>
+          <t>90,32; 98,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,56; 99,36</t>
+          <t>94,4; 99,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,0; 98,81</t>
+          <t>92,89; 98,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,98; 99,26</t>
+          <t>93,99; 99,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>89,12; 96,06</t>
+          <t>89,34; 95,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>94,79; 99,07</t>
+          <t>94,3; 98,99</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>94,73; 98,92</t>
+          <t>95,11; 98,92</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>93,69; 98,47</t>
+          <t>93,6; 98,36</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>90,82; 96,0</t>
+          <t>91,24; 96,2</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,71%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>87,9; 92,66</t>
+          <t>87,93; 92,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>91,05; 94,98</t>
+          <t>91,06; 95,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89,31; 93,25</t>
+          <t>88,97; 93,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86,85; 92,21</t>
+          <t>86,55; 91,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>91,97; 95,12</t>
+          <t>92,06; 95,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>94,5; 97,09</t>
+          <t>94,59; 97,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>92,14; 95,21</t>
+          <t>92,32; 95,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>88,34; 92,73</t>
+          <t>88,17; 91,59</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>91,11; 93,78</t>
+          <t>91,35; 93,88</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>93,64; 95,81</t>
+          <t>93,64; 95,84</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91,38; 93,86</t>
+          <t>91,39; 93,85</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>88,34; 91,69</t>
+          <t>88,18; 91,02</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26270</t>
+          <t>23328</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>50552</t>
+          <t>60376</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76822</t>
+          <t>83704</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>44624; 54240</t>
+          <t>43063; 54241</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>43884; 55003</t>
+          <t>44135; 54993</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55780; 65123</t>
+          <t>56789; 65083</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14469; 31210</t>
+          <t>14106; 28233</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>72704; 82834</t>
+          <t>73403; 82823</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89133; 97241</t>
+          <t>88329; 97227</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>85462; 92414</t>
+          <t>85641; 92411</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>43741; 53944</t>
+          <t>53206; 63673</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>121014; 135127</t>
+          <t>121337; 135332</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136429; 150286</t>
+          <t>135604; 150273</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>145240; 156451</t>
+          <t>145440; 156480</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>64127; 82733</t>
+          <t>71076; 89957</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>68602</t>
+          <t>71899</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>151127</t>
+          <t>95772</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>219729</t>
+          <t>167670</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51374; 65710</t>
+          <t>51593; 65659</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87694; 97591</t>
+          <t>88265; 97548</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66016; 81035</t>
+          <t>65186; 81026</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57498; 74806</t>
+          <t>61897; 78052</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>125104; 140960</t>
+          <t>125435; 141080</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>143470; 154677</t>
+          <t>142479; 155336</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>131238; 146638</t>
+          <t>132189; 147047</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>136572; 163757</t>
+          <t>87109; 102287</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181759; 203876</t>
+          <t>183476; 204289</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>235878; 250080</t>
+          <t>236116; 250959</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>202950; 225459</t>
+          <t>202713; 224227</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>201917; 234981</t>
+          <t>154509; 176864</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70649</t>
+          <t>77058</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>103318</t>
+          <t>118339</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>173965</t>
+          <t>195397</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>76610; 88507</t>
+          <t>76227; 88387</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>107888; 120067</t>
+          <t>108629; 120287</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>126798; 140781</t>
+          <t>126255; 140790</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63226; 75767</t>
+          <t>67416; 84168</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>165112; 179066</t>
+          <t>164673; 179105</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>166840; 184149</t>
+          <t>167075; 184052</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>146752; 161830</t>
+          <t>146705; 161747</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>96962; 108685</t>
+          <t>111131; 123498</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>245751; 265103</t>
+          <t>246373; 265601</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>280641; 301485</t>
+          <t>282055; 302196</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>279881; 299763</t>
+          <t>279162; 299461</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>163710; 182290</t>
+          <t>183470; 204048</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>110592</t>
+          <t>123886</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>145321</t>
+          <t>153817</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>255913</t>
+          <t>277703</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>59476; 72328</t>
+          <t>59593; 72882</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>89873; 105314</t>
+          <t>91219; 105431</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>131541; 149856</t>
+          <t>131030; 149822</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>101041; 117080</t>
+          <t>114711; 130884</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>128528; 141435</t>
+          <t>128549; 142119</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>183003; 190486</t>
+          <t>182164; 190475</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>156754; 172158</t>
+          <t>156059; 171190</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>138115; 151516</t>
+          <t>145928; 160152</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>193968; 211426</t>
+          <t>193134; 211663</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>278388; 294930</t>
+          <t>278404; 294350</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>293446; 317239</t>
+          <t>295069; 318239</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>244298; 265296</t>
+          <t>266638; 288108</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128417</t>
+          <t>131725</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>124261</t>
+          <t>142242</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>252678</t>
+          <t>273967</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>107247; 120668</t>
+          <t>107702; 120584</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>108542; 123449</t>
+          <t>108285; 123471</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>123083; 136776</t>
+          <t>123075; 136894</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>121662; 133378</t>
+          <t>124593; 136650</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>130811; 144387</t>
+          <t>130442; 144819</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>149354; 157694</t>
+          <t>148409; 157719</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>167475; 183109</t>
+          <t>166911; 183113</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>118048; 129050</t>
+          <t>135725; 147479</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>244511; 262641</t>
+          <t>243290; 261716</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>262490; 279237</t>
+          <t>262481; 279213</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>296631; 317051</t>
+          <t>297003; 316964</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>244312; 260108</t>
+          <t>264601; 280992</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>94262</t>
+          <t>104565</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>115247</t>
+          <t>127513</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>209510</t>
+          <t>232077</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>121530; 131307</t>
+          <t>122401; 131299</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>120197; 132069</t>
+          <t>119257; 132150</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>119203; 127323</t>
+          <t>118702; 127247</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>88157; 98499</t>
+          <t>97459; 109187</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>150447; 159500</t>
+          <t>150510; 159380</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>137879; 148015</t>
+          <t>137856; 148002</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>166990; 180094</t>
+          <t>166876; 180197</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>110702; 118505</t>
+          <t>122637; 131020</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>276672; 289654</t>
+          <t>276531; 289119</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>263148; 279087</t>
+          <t>262795; 278240</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>290236; 305851</t>
+          <t>290277; 305822</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>202998; 215486</t>
+          <t>224878; 238425</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>76396</t>
+          <t>85541</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>119500</t>
+          <t>134777</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>195897</t>
+          <t>220318</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>83634; 92299</t>
+          <t>83937; 92299</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>107343; 112239</t>
+          <t>107427; 112239</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>93468; 104436</t>
+          <t>93817; 104286</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>71945; 78850</t>
+          <t>81185; 88333</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>159008; 167091</t>
+          <t>158742; 167084</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>174044; 184922</t>
+          <t>173829; 184244</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>159477; 170252</t>
+          <t>161217; 170266</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>114281; 123176</t>
+          <t>129138; 138728</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>247741; 258923</t>
+          <t>246472; 258716</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>283592; 296140</t>
+          <t>284734; 296158</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>260125; 273398</t>
+          <t>259880; 273095</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>189469; 200288</t>
+          <t>213900; 225534</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>575187</t>
+          <t>618001</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>809327</t>
+          <t>832836</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1384514</t>
+          <t>1450837</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>576484; 607664</t>
+          <t>576662; 607753</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>700016; 730239</t>
+          <t>700099; 731373</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>753571; 786816</t>
+          <t>750704; 786560</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>557031; 591366</t>
+          <t>597741; 634600</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>964140; 997163</t>
+          <t>965119; 997968</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1074049; 1103455</t>
+          <t>1075045; 1103089</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1052613; 1087723</t>
+          <t>1054730; 1088154</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>792039; 831417</t>
+          <t>817036; 848645</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1552659; 1598206</t>
+          <t>1556823; 1599828</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1784283; 1825624</t>
+          <t>1784250; 1826164</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1815051; 1864231</t>
+          <t>1815344; 1864046</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1358544; 1410118</t>
+          <t>1426064; 1471984</t>
         </is>
       </c>
     </row>
